--- a/docs/release/testing/staging_validation_test_cases.xlsx
+++ b/docs/release/testing/staging_validation_test_cases.xlsx
@@ -928,7 +928,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>admin@promoshake.net / Admin1234!</t>
+          <t>Super admin credentials from the staging owner (never versioned)</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>admin@promoshake.net  /  Admin1234!</t>
+          <t>super admin credentials: ask the staging owner (never versioned)</t>
         </is>
       </c>
     </row>
